--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_2/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_2/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -1033,7 +1033,7 @@
     <t>0.0001,0.0053,0.4962,0.9040</t>
   </si>
   <si>
-    <t>0.0001,0.0005,0.9505,0.4527</t>
+    <t>0.0001,0.0005,0.9504,0.4527</t>
   </si>
   <si>
     <t>0.0000,0.0013,0.0043,0.9998</t>

--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_2/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_2/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -859,7 +859,7 @@
     <t>0.0000,0.0010,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0000,0.0614,0.0000,1.0000</t>
+    <t>0.0000,0.0615,0.0000,1.0000</t>
   </si>
   <si>
     <t>0.0000,0.0007,0.0000,1.0000</t>
@@ -886,10 +886,10 @@
     <t>0.0000,0.0077,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0000,0.4490,0.0024,0.9936</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.7845,0.8748</t>
+    <t>0.0000,0.4495,0.0024,0.9936</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.7846,0.8746</t>
   </si>
   <si>
     <t>0.0000,0.0057,0.0030,0.9997</t>
@@ -898,19 +898,19 @@
     <t>0.0000,0.0042,0.0004,1.0000</t>
   </si>
   <si>
-    <t>0.0000,0.9703,0.0005,0.9136</t>
+    <t>0.0000,0.9703,0.0005,0.9135</t>
   </si>
   <si>
     <t>0.0000,0.0014,0.0081,0.9997</t>
   </si>
   <si>
-    <t>0.0000,0.5406,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.1786,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.2713,0.0000,1.0000</t>
+    <t>0.0000,0.5410,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.1787,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.2714,0.0000,1.0000</t>
   </si>
   <si>
     <t>0.0000,0.0024,0.0063,0.9997</t>
@@ -928,19 +928,19 @@
     <t>0.0000,0.0051,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0001,0.9800,0.0211,0.3679</t>
-  </si>
-  <si>
-    <t>0.0000,0.0014,0.5104,0.9439</t>
+    <t>0.0001,0.9800,0.0211,0.3677</t>
+  </si>
+  <si>
+    <t>0.0000,0.0014,0.5107,0.9438</t>
   </si>
   <si>
     <t>0.0000,0.0019,0.0107,0.9995</t>
   </si>
   <si>
-    <t>0.0003,0.8340,0.3846,0.0776</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9850,0.2066</t>
+    <t>0.0003,0.8341,0.3846,0.0775</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9850,0.2065</t>
   </si>
   <si>
     <t>0.0000,0.0046,0.0000,1.0000</t>
@@ -949,25 +949,25 @@
     <t>0.0000,0.9941,0.0000,0.9956</t>
   </si>
   <si>
-    <t>0.0000,0.0876,0.0223,0.9920</t>
-  </si>
-  <si>
-    <t>0.0001,0.0689,0.4031,0.7258</t>
-  </si>
-  <si>
-    <t>0.0000,0.9968,0.0040,0.2485</t>
-  </si>
-  <si>
-    <t>0.0000,0.2181,0.0080,0.9945</t>
+    <t>0.0000,0.0877,0.0223,0.9920</t>
+  </si>
+  <si>
+    <t>0.0001,0.0690,0.4031,0.7256</t>
+  </si>
+  <si>
+    <t>0.0000,0.9968,0.0040,0.2483</t>
+  </si>
+  <si>
+    <t>0.0000,0.2184,0.0080,0.9945</t>
   </si>
   <si>
     <t>0.0000,0.0015,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0001,0.8884,0.0252,0.6935</t>
-  </si>
-  <si>
-    <t>0.0001,0.0143,0.4825,0.8418</t>
+    <t>0.0001,0.8886,0.0252,0.6931</t>
+  </si>
+  <si>
+    <t>0.0001,0.0143,0.4826,0.8416</t>
   </si>
   <si>
     <t>0.0000,0.0667,0.0007,0.9998</t>
@@ -976,16 +976,16 @@
     <t>0.0000,0.0357,0.0192,0.9960</t>
   </si>
   <si>
-    <t>0.0003,0.8638,0.3088,0.1046</t>
-  </si>
-  <si>
-    <t>0.0000,0.1080,0.0031,0.9986</t>
+    <t>0.0003,0.8639,0.3087,0.1045</t>
+  </si>
+  <si>
+    <t>0.0000,0.1082,0.0031,0.9986</t>
   </si>
   <si>
     <t>0.0000,0.0004,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0644,0.0019,0.0383,0.7435</t>
+    <t>0.0644,0.0019,0.0383,0.7434</t>
   </si>
   <si>
     <t>0.0000,0.0012,0.0000,1.0000</t>
@@ -1009,16 +1009,16 @@
     <t>0.0000,0.0030,0.0002,1.0000</t>
   </si>
   <si>
-    <t>0.0000,0.6543,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.5817,0.0000,1.0000</t>
+    <t>0.0000,0.6546,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.5821,0.0000,1.0000</t>
   </si>
   <si>
     <t>0.0000,0.0080,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0000,0.7097,0.0000,0.9997</t>
+    <t>0.0000,0.7100,0.0000,0.9997</t>
   </si>
   <si>
     <t>0.0000,0.0033,0.0000,1.0000</t>
@@ -1030,16 +1030,16 @@
     <t>0.0000,0.0427,0.0030,0.9993</t>
   </si>
   <si>
-    <t>0.0001,0.0053,0.4962,0.9040</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.9504,0.4527</t>
+    <t>0.0001,0.0053,0.4962,0.9039</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.9505,0.4526</t>
   </si>
   <si>
     <t>0.0000,0.0013,0.0043,0.9998</t>
   </si>
   <si>
-    <t>0.0000,0.0533,0.0346,0.9885</t>
+    <t>0.0000,0.0533,0.0346,0.9884</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.0003,1.0000</t>
@@ -1069,7 +1069,7 @@
     <t>0.0000,0.0042,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0000,0.0058,0.0000,1.0000</t>
+    <t>0.0000,0.0059,0.0000,1.0000</t>
   </si>
   <si>
     <t>0.0000,0.0069,0.0000,1.0000</t>
@@ -1084,25 +1084,25 @@
     <t>0.0000,0.0002,0.0001,1.0000</t>
   </si>
   <si>
-    <t>0.0003,0.0159,0.0797,0.9854</t>
+    <t>0.0003,0.0159,0.0798,0.9854</t>
   </si>
   <si>
     <t>0.0000,0.0030,0.0014,0.9999</t>
   </si>
   <si>
-    <t>0.0001,0.0010,0.4061,0.9678</t>
+    <t>0.0001,0.0010,0.4063,0.9677</t>
   </si>
   <si>
     <t>0.0000,0.0002,0.0027,0.9999</t>
   </si>
   <si>
-    <t>0.0000,0.0000,0.3881,0.9949</t>
+    <t>0.0000,0.0000,0.3882,0.9949</t>
   </si>
   <si>
     <t>0.0000,0.0098,0.0002,0.9999</t>
   </si>
   <si>
-    <t>0.0000,0.0000,0.9725,0.6669</t>
+    <t>0.0000,0.0000,0.9725,0.6665</t>
   </si>
   <si>
     <t>0.0000,0.0074,0.0033,0.9996</t>
@@ -1111,7 +1111,7 @@
     <t>0.0000,0.0027,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0000,0.0642,0.0002,0.9999</t>
+    <t>0.0000,0.0643,0.0002,0.9999</t>
   </si>
   <si>
     <t>0.0000,0.0012,0.0025,0.9999</t>
@@ -1126,7 +1126,7 @@
     <t>0.0000,0.0001,0.0002,1.0000</t>
   </si>
   <si>
-    <t>0.0001,0.0001,0.5343,0.9799</t>
+    <t>0.0001,0.0001,0.5346,0.9799</t>
   </si>
   <si>
     <t>0.0000,0.0017,0.0000,1.0000</t>
